--- a/251211/NMDAR_Brainstem_Binary_Results_Table.xlsx
+++ b/251211/NMDAR_Brainstem_Binary_Results_Table.xlsx
@@ -383,11 +383,11 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9994</v>
+        <v>0.9938</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.9801 – 1.0189</t>
+          <t>0.8177 – 1.2058</t>
         </is>
       </c>
       <c r="D2">
@@ -401,11 +401,11 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.9982</v>
+        <v>0.9823</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.9801 – 1.0165</t>
+          <t>0.8175 – 1.1776</t>
         </is>
       </c>
       <c r="D3">
@@ -419,11 +419,11 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.9912</v>
+        <v>0.9155</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.9739 – 1.0083</t>
+          <t>0.7678 – 1.0864</t>
         </is>
       </c>
       <c r="D4">
@@ -437,11 +437,11 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9891</v>
+        <v>0.8958</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.9725 – 1.0055</t>
+          <t>0.7565 – 1.0566</t>
         </is>
       </c>
       <c r="D5">
@@ -455,11 +455,11 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.7671</v>
+        <v>0.9738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.1517 – 3.7068</t>
+          <t>0.8281 – 1.14</t>
         </is>
       </c>
       <c r="D6">
@@ -473,11 +473,11 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.4248</v>
+        <v>0.9179</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0914 – 1.7906</t>
+          <t>0.7872 – 1.06</t>
         </is>
       </c>
       <c r="D7">
@@ -491,11 +491,11 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.3408</v>
+        <v>0.8979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0796 – 1.3573</t>
+          <t>0.7764 – 1.031</t>
         </is>
       </c>
       <c r="D8">
@@ -509,11 +509,11 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.4734</v>
+        <v>0.928</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.118 – 1.7943</t>
+          <t>0.8076 – 1.0602</t>
         </is>
       </c>
       <c r="D9">
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.9947</v>
+        <v>0.9478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.973 – 1.0164</t>
+          <t>0.7607 – 1.1761</t>
         </is>
       </c>
       <c r="D10">
@@ -545,11 +545,11 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.9885</v>
+        <v>0.8907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.968 – 1.0088</t>
+          <t>0.7224 – 1.0916</t>
         </is>
       </c>
       <c r="D11">
@@ -563,11 +563,11 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.9791</v>
+        <v>0.8096</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.959 – 0.9987</t>
+          <t>0.6576 – 0.9873</t>
         </is>
       </c>
       <c r="D12">
@@ -581,11 +581,11 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.9813</v>
+        <v>0.8276</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.9618 – 1.0003</t>
+          <t>0.6775 – 1.0027</t>
         </is>
       </c>
       <c r="D13">
@@ -599,11 +599,11 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.9947</v>
+        <v>0.9479</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.9785 – 1.0107</t>
+          <t>0.8044 – 1.1127</t>
         </is>
       </c>
       <c r="D14">
@@ -617,11 +617,11 @@
         </is>
       </c>
       <c r="B15">
-        <v>1.0029</v>
+        <v>1.0289</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.9858 – 1.0201</t>
+          <t>0.8671 – 1.2203</t>
         </is>
       </c>
       <c r="D15">
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.0064</v>
+        <v>1.0659</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.9905 – 1.0226</t>
+          <t>0.9091 – 1.2502</t>
         </is>
       </c>
       <c r="D16">
@@ -653,11 +653,11 @@
         </is>
       </c>
       <c r="B17">
-        <v>1.0025</v>
+        <v>1.0249</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.9867 – 1.0184</t>
+          <t>0.8745 – 1.1997</t>
         </is>
       </c>
       <c r="D17">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.0018</v>
+        <v>1.0181</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.9854 – 1.0184</t>
+          <t>0.8629 – 1.2001</t>
         </is>
       </c>
       <c r="D18">
@@ -689,11 +689,11 @@
         </is>
       </c>
       <c r="B19">
-        <v>1.0012</v>
+        <v>1.0124</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.9859 – 1.0166</t>
+          <t>0.8679 – 1.179</t>
         </is>
       </c>
       <c r="D19">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.9923</v>
+        <v>0.9258</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.9772 – 1.0073</t>
+          <t>0.7939 – 1.075</t>
         </is>
       </c>
       <c r="D20">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.9881</v>
+        <v>0.8871</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.9735 – 1.0025</t>
+          <t>0.7642 – 1.0254</t>
         </is>
       </c>
       <c r="D21">
@@ -743,11 +743,11 @@
         </is>
       </c>
       <c r="B22">
-        <v>1.0009</v>
+        <v>1.0093</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.9769 – 1.0253</t>
+          <t>0.7914 – 1.2842</t>
         </is>
       </c>
       <c r="D22">
@@ -761,11 +761,11 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.9961</v>
+        <v>0.9615</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.9735 – 1.0188</t>
+          <t>0.7645 – 1.2049</t>
         </is>
       </c>
       <c r="D23">
@@ -779,11 +779,11 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.9898</v>
+        <v>0.9029</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.9689 – 1.0105</t>
+          <t>0.7292 – 1.1105</t>
         </is>
       </c>
       <c r="D24">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.9887</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.9685 – 1.0087</t>
+          <t>0.7262 – 1.091</t>
         </is>
       </c>
       <c r="D25">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="B26">
-        <v>1.002</v>
+        <v>1.0205</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.9856 – 1.0186</t>
+          <t>0.8654 – 1.2024</t>
         </is>
       </c>
       <c r="D26">
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.0006</v>
+        <v>1.0057</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.9853 – 1.0159</t>
+          <t>0.8624 – 1.1707</t>
         </is>
       </c>
       <c r="D27">
@@ -851,11 +851,11 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.9922</v>
+        <v>0.9247</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.9771 – 1.0071</t>
+          <t>0.7933 – 1.0731</t>
         </is>
       </c>
       <c r="D28">
@@ -869,11 +869,11 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.9876</v>
+        <v>0.8823</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.9729 – 1.002</t>
+          <t>0.7598 – 1.0201</t>
         </is>
       </c>
       <c r="D29">
